--- a/public/post/drafts/season-prediction/men_points-predictions-missing-races.xlsx
+++ b/public/post/drafts/season-prediction/men_points-predictions-missing-races.xlsx
@@ -510,34 +510,34 @@
         <v>2808.02610510736</v>
       </c>
       <c r="C2" t="n">
-        <v>2721.72635272848</v>
+        <v>2721.20407336117</v>
       </c>
       <c r="D2" t="n">
-        <v>2635.01667296529</v>
+        <v>2636.2013448803</v>
       </c>
       <c r="E2" t="n">
-        <v>2548.92353273039</v>
+        <v>2548.24905986802</v>
       </c>
       <c r="F2" t="n">
-        <v>2462.85052388128</v>
+        <v>2461.99678006366</v>
       </c>
       <c r="G2" t="n">
-        <v>2375.08233598945</v>
+        <v>2374.47788907117</v>
       </c>
       <c r="H2" t="n">
-        <v>2288.10314239722</v>
+        <v>2288.84066137835</v>
       </c>
       <c r="I2" t="n">
-        <v>2203.12293243864</v>
+        <v>2201.50415251442</v>
       </c>
       <c r="J2" t="n">
-        <v>2115.41240535579</v>
+        <v>2115.34801975274</v>
       </c>
       <c r="K2" t="n">
-        <v>2029.58224113707</v>
+        <v>2028.60711015325</v>
       </c>
       <c r="L2" t="n">
-        <v>1942.48067151694</v>
+        <v>1942.57922623981</v>
       </c>
     </row>
     <row r="3">
@@ -548,34 +548,34 @@
         <v>2040.78676284599</v>
       </c>
       <c r="C3" t="n">
-        <v>1981.40570645237</v>
+        <v>1980.41977325444</v>
       </c>
       <c r="D3" t="n">
-        <v>1920.18366588125</v>
+        <v>1918.39223052706</v>
       </c>
       <c r="E3" t="n">
-        <v>1855.47685476502</v>
+        <v>1855.89646886464</v>
       </c>
       <c r="F3" t="n">
-        <v>1795.03720356448</v>
+        <v>1795.6863404766</v>
       </c>
       <c r="G3" t="n">
-        <v>1731.20690524755</v>
+        <v>1733.17545953008</v>
       </c>
       <c r="H3" t="n">
-        <v>1667.99203357769</v>
+        <v>1675.90092091651</v>
       </c>
       <c r="I3" t="n">
-        <v>1609.65314945571</v>
+        <v>1606.68385959762</v>
       </c>
       <c r="J3" t="n">
-        <v>1548.69787394031</v>
+        <v>1552.82045190612</v>
       </c>
       <c r="K3" t="n">
-        <v>1483.83561769134</v>
+        <v>1483.47447275949</v>
       </c>
       <c r="L3" t="n">
-        <v>1430.39310324203</v>
+        <v>1429.75671537389</v>
       </c>
     </row>
     <row r="4">
@@ -586,34 +586,34 @@
         <v>2039.96170447067</v>
       </c>
       <c r="C4" t="n">
-        <v>1975.17574498338</v>
+        <v>1975.20097078732</v>
       </c>
       <c r="D4" t="n">
-        <v>1908.2441947281</v>
+        <v>1906.26433055637</v>
       </c>
       <c r="E4" t="n">
-        <v>1844.52334496116</v>
+        <v>1844.4454906081</v>
       </c>
       <c r="F4" t="n">
-        <v>1782.05542968358</v>
+        <v>1779.06709776689</v>
       </c>
       <c r="G4" t="n">
-        <v>1712.83604882436</v>
+        <v>1708.41939643131</v>
       </c>
       <c r="H4" t="n">
-        <v>1648.33306128395</v>
+        <v>1646.3616744944</v>
       </c>
       <c r="I4" t="n">
-        <v>1578.35771914515</v>
+        <v>1581.4034204186</v>
       </c>
       <c r="J4" t="n">
-        <v>1521.30076650066</v>
+        <v>1520.23464617207</v>
       </c>
       <c r="K4" t="n">
-        <v>1452.7881323584</v>
+        <v>1460.39021995649</v>
       </c>
       <c r="L4" t="n">
-        <v>1382.09688622845</v>
+        <v>1384.54379323107</v>
       </c>
     </row>
     <row r="5">
@@ -624,34 +624,34 @@
         <v>1888.39353527345</v>
       </c>
       <c r="C5" t="n">
-        <v>1829.52993452397</v>
+        <v>1831.14091130164</v>
       </c>
       <c r="D5" t="n">
-        <v>1771.56378098268</v>
+        <v>1771.04594262968</v>
       </c>
       <c r="E5" t="n">
-        <v>1713.13162979965</v>
+        <v>1716.08494375364</v>
       </c>
       <c r="F5" t="n">
-        <v>1658.25427689804</v>
+        <v>1658.45541130007</v>
       </c>
       <c r="G5" t="n">
-        <v>1599.97468018957</v>
+        <v>1599.66370686781</v>
       </c>
       <c r="H5" t="n">
-        <v>1544.48671503327</v>
+        <v>1535.72755770442</v>
       </c>
       <c r="I5" t="n">
-        <v>1487.33990495043</v>
+        <v>1483.57597744465</v>
       </c>
       <c r="J5" t="n">
-        <v>1417.8110135223</v>
+        <v>1424.0085401891</v>
       </c>
       <c r="K5" t="n">
-        <v>1365.50836545804</v>
+        <v>1359.83568249548</v>
       </c>
       <c r="L5" t="n">
-        <v>1312.96562302587</v>
+        <v>1310.45083709136</v>
       </c>
     </row>
     <row r="6">
@@ -662,34 +662,34 @@
         <v>1660.0628128079</v>
       </c>
       <c r="C6" t="n">
-        <v>1613.13564674885</v>
+        <v>1614.8909081701</v>
       </c>
       <c r="D6" t="n">
-        <v>1556.83529118191</v>
+        <v>1564.08783804715</v>
       </c>
       <c r="E6" t="n">
-        <v>1516.68267164177</v>
+        <v>1518.66436744812</v>
       </c>
       <c r="F6" t="n">
-        <v>1460.7901839349</v>
+        <v>1466.37799498724</v>
       </c>
       <c r="G6" t="n">
-        <v>1431.22743262254</v>
+        <v>1414.63997191744</v>
       </c>
       <c r="H6" t="n">
-        <v>1374.92555463776</v>
+        <v>1362.73448836961</v>
       </c>
       <c r="I6" t="n">
-        <v>1328.9511588456</v>
+        <v>1317.27095779065</v>
       </c>
       <c r="J6" t="n">
-        <v>1278.04916081029</v>
+        <v>1264.0209894882</v>
       </c>
       <c r="K6" t="n">
-        <v>1224.86606790192</v>
+        <v>1230.49530204456</v>
       </c>
       <c r="L6" t="n">
-        <v>1184.53169754721</v>
+        <v>1186.01942094538</v>
       </c>
     </row>
     <row r="7">
@@ -700,34 +700,34 @@
         <v>1540.82638789349</v>
       </c>
       <c r="C7" t="n">
-        <v>1496.77352401751</v>
+        <v>1495.55856324787</v>
       </c>
       <c r="D7" t="n">
-        <v>1447.77050812295</v>
+        <v>1449.82529980204</v>
       </c>
       <c r="E7" t="n">
-        <v>1399.30255866939</v>
+        <v>1403.99843877643</v>
       </c>
       <c r="F7" t="n">
-        <v>1357.57255060138</v>
+        <v>1359.69772756637</v>
       </c>
       <c r="G7" t="n">
-        <v>1315.75941279333</v>
+        <v>1312.7223974742</v>
       </c>
       <c r="H7" t="n">
-        <v>1273.29034179856</v>
+        <v>1270.84353815044</v>
       </c>
       <c r="I7" t="n">
-        <v>1223.673514406</v>
+        <v>1234.43245634671</v>
       </c>
       <c r="J7" t="n">
-        <v>1175.96111444657</v>
+        <v>1178.90544102178</v>
       </c>
       <c r="K7" t="n">
-        <v>1139.44724645002</v>
+        <v>1141.02264382231</v>
       </c>
       <c r="L7" t="n">
-        <v>1075.15265664503</v>
+        <v>1092.21830848772</v>
       </c>
     </row>
     <row r="8">
@@ -738,34 +738,34 @@
         <v>1526.46647607068</v>
       </c>
       <c r="C8" t="n">
-        <v>1478.14706667096</v>
+        <v>1479.39377089486</v>
       </c>
       <c r="D8" t="n">
-        <v>1429.61814702447</v>
+        <v>1432.208200413</v>
       </c>
       <c r="E8" t="n">
-        <v>1380.07402904175</v>
+        <v>1381.01308878355</v>
       </c>
       <c r="F8" t="n">
-        <v>1331.03609552585</v>
+        <v>1333.25635656622</v>
       </c>
       <c r="G8" t="n">
-        <v>1281.04675540528</v>
+        <v>1288.82393892371</v>
       </c>
       <c r="H8" t="n">
-        <v>1235.35710739104</v>
+        <v>1235.26604397402</v>
       </c>
       <c r="I8" t="n">
-        <v>1185.70438779665</v>
+        <v>1187.35753379887</v>
       </c>
       <c r="J8" t="n">
-        <v>1136.7152121506</v>
+        <v>1137.45890317622</v>
       </c>
       <c r="K8" t="n">
-        <v>1085.27755902913</v>
+        <v>1087.12809757946</v>
       </c>
       <c r="L8" t="n">
-        <v>1043.36768421806</v>
+        <v>1043.24283716027</v>
       </c>
     </row>
     <row r="9">
@@ -776,34 +776,34 @@
         <v>1361.3264147519</v>
       </c>
       <c r="C9" t="n">
-        <v>1319.04351948353</v>
+        <v>1315.92660523165</v>
       </c>
       <c r="D9" t="n">
-        <v>1281.79750527032</v>
+        <v>1276.39325597986</v>
       </c>
       <c r="E9" t="n">
-        <v>1239.77204536298</v>
+        <v>1236.53967602215</v>
       </c>
       <c r="F9" t="n">
-        <v>1200.33437110927</v>
+        <v>1196.65232296247</v>
       </c>
       <c r="G9" t="n">
-        <v>1160.09423682575</v>
+        <v>1155.07244590222</v>
       </c>
       <c r="H9" t="n">
-        <v>1118.09663526793</v>
+        <v>1121.71653606205</v>
       </c>
       <c r="I9" t="n">
-        <v>1068.63097328653</v>
+        <v>1084.47219385475</v>
       </c>
       <c r="J9" t="n">
-        <v>1045.63747077412</v>
+        <v>1038.61985493259</v>
       </c>
       <c r="K9" t="n">
-        <v>1001.39688451372</v>
+        <v>1000.310717185</v>
       </c>
       <c r="L9" t="n">
-        <v>957.099344847641</v>
+        <v>963.370020314167</v>
       </c>
     </row>
     <row r="10">
@@ -814,34 +814,34 @@
         <v>1347.54069216612</v>
       </c>
       <c r="C10" t="n">
-        <v>1303.32183885619</v>
+        <v>1303.14446001861</v>
       </c>
       <c r="D10" t="n">
-        <v>1260.7855748126</v>
+        <v>1263.95162481313</v>
       </c>
       <c r="E10" t="n">
-        <v>1219.57325191772</v>
+        <v>1217.25558188114</v>
       </c>
       <c r="F10" t="n">
-        <v>1181.23742676672</v>
+        <v>1174.08618982739</v>
       </c>
       <c r="G10" t="n">
-        <v>1134.72129759629</v>
+        <v>1131.03297298169</v>
       </c>
       <c r="H10" t="n">
-        <v>1091.38551553236</v>
+        <v>1096.20753200986</v>
       </c>
       <c r="I10" t="n">
-        <v>1052.72547548409</v>
+        <v>1052.20442567584</v>
       </c>
       <c r="J10" t="n">
-        <v>1011.90623819544</v>
+        <v>1008.30182381837</v>
       </c>
       <c r="K10" t="n">
-        <v>966.613746718583</v>
+        <v>965.623725988372</v>
       </c>
       <c r="L10" t="n">
-        <v>921.099971963037</v>
+        <v>920.810896066035</v>
       </c>
     </row>
     <row r="11">
@@ -852,34 +852,34 @@
         <v>1242.56353323432</v>
       </c>
       <c r="C11" t="n">
-        <v>1204.26357783097</v>
+        <v>1204.03063066585</v>
       </c>
       <c r="D11" t="n">
-        <v>1166.78844819785</v>
+        <v>1163.13302615649</v>
       </c>
       <c r="E11" t="n">
-        <v>1124.90353025207</v>
+        <v>1125.66412491399</v>
       </c>
       <c r="F11" t="n">
-        <v>1086.17409859213</v>
+        <v>1087.05768349709</v>
       </c>
       <c r="G11" t="n">
-        <v>1045.39675855862</v>
+        <v>1049.66907064249</v>
       </c>
       <c r="H11" t="n">
-        <v>1007.63137082692</v>
+        <v>1006.7382854323</v>
       </c>
       <c r="I11" t="n">
-        <v>969.666150302939</v>
+        <v>968.092641714824</v>
       </c>
       <c r="J11" t="n">
-        <v>928.518364761384</v>
+        <v>932.722622562248</v>
       </c>
       <c r="K11" t="n">
-        <v>890.814869264496</v>
+        <v>893.539505493228</v>
       </c>
       <c r="L11" t="n">
-        <v>853.294567962845</v>
+        <v>854.453817548796</v>
       </c>
     </row>
     <row r="12">
@@ -890,34 +890,34 @@
         <v>1234.99226848089</v>
       </c>
       <c r="C12" t="n">
-        <v>1195.10982227548</v>
+        <v>1201.59404738727</v>
       </c>
       <c r="D12" t="n">
-        <v>1165.32810351384</v>
+        <v>1162.4126654567</v>
       </c>
       <c r="E12" t="n">
-        <v>1128.7201323673</v>
+        <v>1126.87836309722</v>
       </c>
       <c r="F12" t="n">
-        <v>1092.25010159004</v>
+        <v>1100.43156022709</v>
       </c>
       <c r="G12" t="n">
-        <v>1060.62287737123</v>
+        <v>1058.69227169363</v>
       </c>
       <c r="H12" t="n">
-        <v>1027.63646955</v>
+        <v>1024.55350827083</v>
       </c>
       <c r="I12" t="n">
-        <v>985.22598902932</v>
+        <v>992.2332717248</v>
       </c>
       <c r="J12" t="n">
-        <v>953.795846584704</v>
+        <v>950.814089421185</v>
       </c>
       <c r="K12" t="n">
-        <v>901.834022264439</v>
+        <v>916.369101014498</v>
       </c>
       <c r="L12" t="n">
-        <v>886.406548664219</v>
+        <v>880.126172749296</v>
       </c>
     </row>
     <row r="13">
@@ -928,34 +928,34 @@
         <v>1202.31328769293</v>
       </c>
       <c r="C13" t="n">
-        <v>1170.26555098699</v>
+        <v>1167.61075976274</v>
       </c>
       <c r="D13" t="n">
-        <v>1128.13437590741</v>
+        <v>1132.54207445166</v>
       </c>
       <c r="E13" t="n">
-        <v>1090.7261978885</v>
+        <v>1094.61531412431</v>
       </c>
       <c r="F13" t="n">
-        <v>1059.98746882187</v>
+        <v>1066.45926585449</v>
       </c>
       <c r="G13" t="n">
-        <v>1020.73096176862</v>
+        <v>1016.94299435362</v>
       </c>
       <c r="H13" t="n">
-        <v>996.047557466613</v>
+        <v>992.267421213921</v>
       </c>
       <c r="I13" t="n">
-        <v>953.096967940879</v>
+        <v>955.739342034641</v>
       </c>
       <c r="J13" t="n">
-        <v>918.551537215043</v>
+        <v>917.119148644992</v>
       </c>
       <c r="K13" t="n">
-        <v>874.911754239696</v>
+        <v>888.506221883394</v>
       </c>
       <c r="L13" t="n">
-        <v>849.720667389102</v>
+        <v>850.690975010963</v>
       </c>
     </row>
     <row r="14">
@@ -966,34 +966,34 @@
         <v>1178.18007576861</v>
       </c>
       <c r="C14" t="n">
-        <v>1145.33630548981</v>
+        <v>1149.25984179875</v>
       </c>
       <c r="D14" t="n">
-        <v>1105.68534312041</v>
+        <v>1109.1284250283</v>
       </c>
       <c r="E14" t="n">
-        <v>1079.13970137686</v>
+        <v>1074.18978397027</v>
       </c>
       <c r="F14" t="n">
-        <v>1045.83276063246</v>
+        <v>1037.80444400099</v>
       </c>
       <c r="G14" t="n">
-        <v>1011.34388693765</v>
+        <v>1012.15775154523</v>
       </c>
       <c r="H14" t="n">
-        <v>979.066723046655</v>
+        <v>969.03774777354</v>
       </c>
       <c r="I14" t="n">
-        <v>937.665846276531</v>
+        <v>938.058512356617</v>
       </c>
       <c r="J14" t="n">
-        <v>912.106503801821</v>
+        <v>910.586737901143</v>
       </c>
       <c r="K14" t="n">
-        <v>876.818265877831</v>
+        <v>871.106058811998</v>
       </c>
       <c r="L14" t="n">
-        <v>831.779931451505</v>
+        <v>841.864810370405</v>
       </c>
     </row>
     <row r="15">
@@ -1004,34 +1004,34 @@
         <v>1174.60071882834</v>
       </c>
       <c r="C15" t="n">
-        <v>1138.50010330671</v>
+        <v>1138.66978444449</v>
       </c>
       <c r="D15" t="n">
-        <v>1100.90436123722</v>
+        <v>1098.46948773922</v>
       </c>
       <c r="E15" t="n">
-        <v>1064.41161150324</v>
+        <v>1061.99824407187</v>
       </c>
       <c r="F15" t="n">
-        <v>1029.85737089614</v>
+        <v>1029.1225943691</v>
       </c>
       <c r="G15" t="n">
-        <v>988.163866385553</v>
+        <v>993.019887605314</v>
       </c>
       <c r="H15" t="n">
-        <v>949.640859934863</v>
+        <v>952.828685394464</v>
       </c>
       <c r="I15" t="n">
-        <v>914.821556437893</v>
+        <v>915.425484804232</v>
       </c>
       <c r="J15" t="n">
-        <v>879.414518904512</v>
+        <v>880.465239430465</v>
       </c>
       <c r="K15" t="n">
-        <v>839.838353391094</v>
+        <v>841.414102735037</v>
       </c>
       <c r="L15" t="n">
-        <v>804.453788537755</v>
+        <v>802.849654862218</v>
       </c>
     </row>
     <row r="16">
@@ -1042,34 +1042,34 @@
         <v>1134.34897803626</v>
       </c>
       <c r="C16" t="n">
-        <v>1101.04029913294</v>
+        <v>1103.23862985353</v>
       </c>
       <c r="D16" t="n">
-        <v>1071.57067215131</v>
+        <v>1069.60567739422</v>
       </c>
       <c r="E16" t="n">
-        <v>1040.17980130909</v>
+        <v>1045.25744552736</v>
       </c>
       <c r="F16" t="n">
-        <v>1013.19699304943</v>
+        <v>1008.19657703898</v>
       </c>
       <c r="G16" t="n">
-        <v>968.380245265172</v>
+        <v>966.09040102538</v>
       </c>
       <c r="H16" t="n">
-        <v>956.774954634456</v>
+        <v>946.725612839016</v>
       </c>
       <c r="I16" t="n">
-        <v>920.537105965786</v>
+        <v>906.458895136417</v>
       </c>
       <c r="J16" t="n">
-        <v>880.321435616696</v>
+        <v>887.991593194193</v>
       </c>
       <c r="K16" t="n">
-        <v>858.835938383973</v>
+        <v>859.842307535884</v>
       </c>
       <c r="L16" t="n">
-        <v>822.412730972825</v>
+        <v>822.713642685804</v>
       </c>
     </row>
     <row r="17">
@@ -1080,34 +1080,34 @@
         <v>1122.64794434291</v>
       </c>
       <c r="C17" t="n">
-        <v>1084.71399351868</v>
+        <v>1086.0818005555</v>
       </c>
       <c r="D17" t="n">
-        <v>1048.11751895853</v>
+        <v>1047.51075871349</v>
       </c>
       <c r="E17" t="n">
-        <v>1010.97703257815</v>
+        <v>1010.83626513693</v>
       </c>
       <c r="F17" t="n">
-        <v>965.118644571115</v>
+        <v>970.712046221903</v>
       </c>
       <c r="G17" t="n">
-        <v>934.991730627519</v>
+        <v>927.176395950587</v>
       </c>
       <c r="H17" t="n">
-        <v>891.257948981943</v>
+        <v>891.150790049376</v>
       </c>
       <c r="I17" t="n">
-        <v>857.853115826788</v>
+        <v>855.787408809814</v>
       </c>
       <c r="J17" t="n">
-        <v>812.288949391933</v>
+        <v>823.331600985334</v>
       </c>
       <c r="K17" t="n">
-        <v>783.777743931684</v>
+        <v>781.820543895814</v>
       </c>
       <c r="L17" t="n">
-        <v>743.953213817219</v>
+        <v>739.916104539711</v>
       </c>
     </row>
     <row r="18">
@@ -1118,34 +1118,34 @@
         <v>1069.99854557875</v>
       </c>
       <c r="C18" t="n">
-        <v>1035.35212344227</v>
+        <v>1034.36296303655</v>
       </c>
       <c r="D18" t="n">
-        <v>997.578326066119</v>
+        <v>1000.91676112199</v>
       </c>
       <c r="E18" t="n">
-        <v>961.434023127032</v>
+        <v>961.955594498704</v>
       </c>
       <c r="F18" t="n">
-        <v>928.616092589036</v>
+        <v>929.001129700575</v>
       </c>
       <c r="G18" t="n">
-        <v>891.310958976968</v>
+        <v>891.494970943221</v>
       </c>
       <c r="H18" t="n">
-        <v>853.857919099783</v>
+        <v>851.840636064939</v>
       </c>
       <c r="I18" t="n">
-        <v>816.981236324347</v>
+        <v>817.883689176043</v>
       </c>
       <c r="J18" t="n">
-        <v>784.078649542035</v>
+        <v>780.308958938863</v>
       </c>
       <c r="K18" t="n">
-        <v>744.184492156018</v>
+        <v>750.082707264198</v>
       </c>
       <c r="L18" t="n">
-        <v>712.028826047665</v>
+        <v>715.981189529519</v>
       </c>
     </row>
     <row r="19">
@@ -1156,34 +1156,34 @@
         <v>1020.0352334958</v>
       </c>
       <c r="C19" t="n">
-        <v>985.365543580315</v>
+        <v>986.452721722328</v>
       </c>
       <c r="D19" t="n">
-        <v>949.690518251762</v>
+        <v>948.321195484662</v>
       </c>
       <c r="E19" t="n">
-        <v>916.129541194884</v>
+        <v>912.362901182933</v>
       </c>
       <c r="F19" t="n">
-        <v>876.244877208772</v>
+        <v>876.407365742666</v>
       </c>
       <c r="G19" t="n">
-        <v>847.063631148702</v>
+        <v>843.511240713775</v>
       </c>
       <c r="H19" t="n">
-        <v>808.966042803686</v>
+        <v>810.51082258929</v>
       </c>
       <c r="I19" t="n">
-        <v>775.466440981952</v>
+        <v>773.482253985725</v>
       </c>
       <c r="J19" t="n">
-        <v>736.768275929569</v>
+        <v>735.922221739741</v>
       </c>
       <c r="K19" t="n">
-        <v>704.343760622214</v>
+        <v>706.014429936099</v>
       </c>
       <c r="L19" t="n">
-        <v>666.609468281723</v>
+        <v>667.621775373609</v>
       </c>
     </row>
     <row r="20">
@@ -1194,34 +1194,34 @@
         <v>1004.73539736046</v>
       </c>
       <c r="C20" t="n">
-        <v>978.403662699578</v>
+        <v>981.259590170144</v>
       </c>
       <c r="D20" t="n">
-        <v>951.683534226475</v>
+        <v>945.40666813779</v>
       </c>
       <c r="E20" t="n">
-        <v>923.870272316969</v>
+        <v>923.319514956567</v>
       </c>
       <c r="F20" t="n">
-        <v>886.562054264313</v>
+        <v>900.106101442616</v>
       </c>
       <c r="G20" t="n">
-        <v>870.180949344153</v>
+        <v>870.168110403175</v>
       </c>
       <c r="H20" t="n">
-        <v>840.350708562998</v>
+        <v>843.279140952534</v>
       </c>
       <c r="I20" t="n">
-        <v>809.070295519959</v>
+        <v>809.85999167052</v>
       </c>
       <c r="J20" t="n">
-        <v>792.173789849004</v>
+        <v>792.033829236801</v>
       </c>
       <c r="K20" t="n">
-        <v>754.813421840494</v>
+        <v>756.598003103945</v>
       </c>
       <c r="L20" t="n">
-        <v>728.014490989498</v>
+        <v>722.51084426847</v>
       </c>
     </row>
     <row r="21">
@@ -1232,34 +1232,34 @@
         <v>1003.14187141868</v>
       </c>
       <c r="C21" t="n">
-        <v>970.914690192239</v>
+        <v>969.810737538707</v>
       </c>
       <c r="D21" t="n">
-        <v>935.919096537421</v>
+        <v>935.513058547079</v>
       </c>
       <c r="E21" t="n">
-        <v>903.125200898823</v>
+        <v>903.417022743009</v>
       </c>
       <c r="F21" t="n">
-        <v>868.542491525405</v>
+        <v>870.347110925831</v>
       </c>
       <c r="G21" t="n">
-        <v>835.947443894528</v>
+        <v>836.179696755271</v>
       </c>
       <c r="H21" t="n">
-        <v>804.131066693283</v>
+        <v>801.996850551697</v>
       </c>
       <c r="I21" t="n">
-        <v>770.428720057445</v>
+        <v>769.832572723218</v>
       </c>
       <c r="J21" t="n">
-        <v>734.836142116598</v>
+        <v>737.396065671541</v>
       </c>
       <c r="K21" t="n">
-        <v>704.076257398948</v>
+        <v>703.293623293814</v>
       </c>
       <c r="L21" t="n">
-        <v>670.860958783931</v>
+        <v>669.939056833678</v>
       </c>
     </row>
     <row r="22">
@@ -1270,34 +1270,34 @@
         <v>992.555423550307</v>
       </c>
       <c r="C22" t="n">
-        <v>965.551528724811</v>
+        <v>964.240818341341</v>
       </c>
       <c r="D22" t="n">
-        <v>944.839004690978</v>
+        <v>938.326254152215</v>
       </c>
       <c r="E22" t="n">
-        <v>917.191831310023</v>
+        <v>921.008046642976</v>
       </c>
       <c r="F22" t="n">
-        <v>889.957588904802</v>
+        <v>888.498033751828</v>
       </c>
       <c r="G22" t="n">
-        <v>856.482724345954</v>
+        <v>861.017968687668</v>
       </c>
       <c r="H22" t="n">
-        <v>822.174186109382</v>
+        <v>835.108888160062</v>
       </c>
       <c r="I22" t="n">
-        <v>796.404713321295</v>
+        <v>812.57218737182</v>
       </c>
       <c r="J22" t="n">
-        <v>777.707706379417</v>
+        <v>781.34297621515</v>
       </c>
       <c r="K22" t="n">
-        <v>746.721641871392</v>
+        <v>747.112478441952</v>
       </c>
       <c r="L22" t="n">
-        <v>727.188285619908</v>
+        <v>717.965316036555</v>
       </c>
     </row>
     <row r="23">
@@ -1308,34 +1308,34 @@
         <v>979.54199267749</v>
       </c>
       <c r="C23" t="n">
-        <v>943.399001128867</v>
+        <v>944.285826904868</v>
       </c>
       <c r="D23" t="n">
-        <v>909.15367173495</v>
+        <v>913.74417225106</v>
       </c>
       <c r="E23" t="n">
-        <v>875.586053809899</v>
+        <v>877.818938341321</v>
       </c>
       <c r="F23" t="n">
-        <v>849.803143048813</v>
+        <v>843.516804791787</v>
       </c>
       <c r="G23" t="n">
-        <v>810.426610813999</v>
+        <v>814.085555892385</v>
       </c>
       <c r="H23" t="n">
-        <v>778.418316848579</v>
+        <v>775.515844947635</v>
       </c>
       <c r="I23" t="n">
-        <v>744.61310504857</v>
+        <v>741.922816279343</v>
       </c>
       <c r="J23" t="n">
-        <v>709.92490417562</v>
+        <v>708.690578775621</v>
       </c>
       <c r="K23" t="n">
-        <v>674.282829124194</v>
+        <v>673.918786441238</v>
       </c>
       <c r="L23" t="n">
-        <v>642.08476289429</v>
+        <v>642.606937322841</v>
       </c>
     </row>
     <row r="24">
@@ -1346,34 +1346,34 @@
         <v>964.250881832494</v>
       </c>
       <c r="C24" t="n">
-        <v>934.156438032509</v>
+        <v>929.773832493247</v>
       </c>
       <c r="D24" t="n">
-        <v>893.151319121291</v>
+        <v>894.988718771313</v>
       </c>
       <c r="E24" t="n">
-        <v>858.013163176044</v>
+        <v>865.15164163597</v>
       </c>
       <c r="F24" t="n">
-        <v>827.743362908706</v>
+        <v>824.546177383369</v>
       </c>
       <c r="G24" t="n">
-        <v>797.431191226075</v>
+        <v>790.191584316469</v>
       </c>
       <c r="H24" t="n">
-        <v>760.690519932907</v>
+        <v>764.86429810839</v>
       </c>
       <c r="I24" t="n">
-        <v>730.44078432787</v>
+        <v>732.365140961077</v>
       </c>
       <c r="J24" t="n">
-        <v>686.474155923972</v>
+        <v>695.773767827421</v>
       </c>
       <c r="K24" t="n">
-        <v>657.752182905037</v>
+        <v>663.609970662378</v>
       </c>
       <c r="L24" t="n">
-        <v>630.076531620372</v>
+        <v>627.270932656516</v>
       </c>
     </row>
     <row r="25">
@@ -1384,34 +1384,34 @@
         <v>963.880381625709</v>
       </c>
       <c r="C25" t="n">
-        <v>935.971956237042</v>
+        <v>931.391871162743</v>
       </c>
       <c r="D25" t="n">
-        <v>900.193533224884</v>
+        <v>898.770669091431</v>
       </c>
       <c r="E25" t="n">
-        <v>857.991572478692</v>
+        <v>857.770603094378</v>
       </c>
       <c r="F25" t="n">
-        <v>825.216035893666</v>
+        <v>821.629373992146</v>
       </c>
       <c r="G25" t="n">
-        <v>805.607338015244</v>
+        <v>798.668912610386</v>
       </c>
       <c r="H25" t="n">
-        <v>763.421362695412</v>
+        <v>755.802783829108</v>
       </c>
       <c r="I25" t="n">
-        <v>731.883167421876</v>
+        <v>728.730854784104</v>
       </c>
       <c r="J25" t="n">
-        <v>696.359461049148</v>
+        <v>706.386348630538</v>
       </c>
       <c r="K25" t="n">
-        <v>668.448464804838</v>
+        <v>660.610653719462</v>
       </c>
       <c r="L25" t="n">
-        <v>637.064992441708</v>
+        <v>644.192885489421</v>
       </c>
     </row>
     <row r="26">
@@ -1422,34 +1422,34 @@
         <v>888.188511102068</v>
       </c>
       <c r="C26" t="n">
-        <v>860.933376975294</v>
+        <v>860.240485174071</v>
       </c>
       <c r="D26" t="n">
-        <v>833.616950888807</v>
+        <v>834.702999407956</v>
       </c>
       <c r="E26" t="n">
-        <v>818.546228041</v>
+        <v>810.914469830248</v>
       </c>
       <c r="F26" t="n">
-        <v>787.996842796109</v>
+        <v>789.940702295519</v>
       </c>
       <c r="G26" t="n">
-        <v>759.809360133664</v>
+        <v>765.18832661084</v>
       </c>
       <c r="H26" t="n">
-        <v>737.057198399787</v>
+        <v>731.848316918498</v>
       </c>
       <c r="I26" t="n">
-        <v>715.961513408227</v>
+        <v>696.252403756181</v>
       </c>
       <c r="J26" t="n">
-        <v>683.269976692026</v>
+        <v>696.049557909918</v>
       </c>
       <c r="K26" t="n">
-        <v>661.984307815943</v>
+        <v>665.523395536893</v>
       </c>
       <c r="L26" t="n">
-        <v>639.005876944311</v>
+        <v>632.304215414379</v>
       </c>
     </row>
     <row r="27">
@@ -1460,34 +1460,34 @@
         <v>857.543624613895</v>
       </c>
       <c r="C27" t="n">
-        <v>823.1859749253</v>
+        <v>826.328568085519</v>
       </c>
       <c r="D27" t="n">
-        <v>806.293336391436</v>
+        <v>795.580366589831</v>
       </c>
       <c r="E27" t="n">
-        <v>762.472819462409</v>
+        <v>756.099867784589</v>
       </c>
       <c r="F27" t="n">
-        <v>731.724459037487</v>
+        <v>730.950457720871</v>
       </c>
       <c r="G27" t="n">
-        <v>704.053732910736</v>
+        <v>703.227651038714</v>
       </c>
       <c r="H27" t="n">
-        <v>677.51421086298</v>
+        <v>670.718503597224</v>
       </c>
       <c r="I27" t="n">
-        <v>659.022624650229</v>
+        <v>635.71074544518</v>
       </c>
       <c r="J27" t="n">
-        <v>614.88035365737</v>
+        <v>614.857639756194</v>
       </c>
       <c r="K27" t="n">
-        <v>581.180957841224</v>
+        <v>582.93347293602</v>
       </c>
       <c r="L27" t="n">
-        <v>557.038184073053</v>
+        <v>554.481122242079</v>
       </c>
     </row>
     <row r="28">
@@ -1498,34 +1498,34 @@
         <v>797.977393715066</v>
       </c>
       <c r="C28" t="n">
-        <v>777.205263757097</v>
+        <v>775.907284229172</v>
       </c>
       <c r="D28" t="n">
-        <v>751.731944970031</v>
+        <v>749.815245969556</v>
       </c>
       <c r="E28" t="n">
-        <v>728.707747727405</v>
+        <v>730.310769156249</v>
       </c>
       <c r="F28" t="n">
-        <v>705.276886086379</v>
+        <v>712.252088738159</v>
       </c>
       <c r="G28" t="n">
-        <v>689.362352777868</v>
+        <v>680.288140861027</v>
       </c>
       <c r="H28" t="n">
-        <v>662.275690616653</v>
+        <v>660.161006070285</v>
       </c>
       <c r="I28" t="n">
-        <v>639.011210918025</v>
+        <v>646.930227451004</v>
       </c>
       <c r="J28" t="n">
-        <v>618.511296341986</v>
+        <v>618.630455593467</v>
       </c>
       <c r="K28" t="n">
-        <v>585.069503607878</v>
+        <v>595.436075514442</v>
       </c>
       <c r="L28" t="n">
-        <v>572.897401416401</v>
+        <v>573.714813353557</v>
       </c>
     </row>
     <row r="29">
@@ -1536,34 +1536,34 @@
         <v>730.591305081265</v>
       </c>
       <c r="C29" t="n">
-        <v>707.011731838949</v>
+        <v>707.21820952544</v>
       </c>
       <c r="D29" t="n">
-        <v>682.50253798408</v>
+        <v>682.01017488549</v>
       </c>
       <c r="E29" t="n">
-        <v>656.949897765059</v>
+        <v>657.046614206938</v>
       </c>
       <c r="F29" t="n">
-        <v>633.5104559127</v>
+        <v>634.327613658089</v>
       </c>
       <c r="G29" t="n">
-        <v>609.272622374473</v>
+        <v>607.769754924012</v>
       </c>
       <c r="H29" t="n">
-        <v>585.879909864041</v>
+        <v>583.929688721694</v>
       </c>
       <c r="I29" t="n">
-        <v>556.800308418416</v>
+        <v>561.262230108624</v>
       </c>
       <c r="J29" t="n">
-        <v>537.553113567694</v>
+        <v>535.03655931362</v>
       </c>
       <c r="K29" t="n">
-        <v>513.727089492135</v>
+        <v>510.935354335947</v>
       </c>
       <c r="L29" t="n">
-        <v>486.078669236153</v>
+        <v>483.383449965433</v>
       </c>
     </row>
     <row r="30">
@@ -1574,34 +1574,34 @@
         <v>718.078699855451</v>
       </c>
       <c r="C30" t="n">
-        <v>691.707087599087</v>
+        <v>692.089367745293</v>
       </c>
       <c r="D30" t="n">
-        <v>668.588615468431</v>
+        <v>668.762284582631</v>
       </c>
       <c r="E30" t="n">
-        <v>647.926884019608</v>
+        <v>634.049859297665</v>
       </c>
       <c r="F30" t="n">
-        <v>620.780546988846</v>
+        <v>610.941531793547</v>
       </c>
       <c r="G30" t="n">
-        <v>592.027091044878</v>
+        <v>590.428623097497</v>
       </c>
       <c r="H30" t="n">
-        <v>550.653441628863</v>
+        <v>550.79447497499</v>
       </c>
       <c r="I30" t="n">
-        <v>528.653196236237</v>
+        <v>527.436925461428</v>
       </c>
       <c r="J30" t="n">
-        <v>497.575000281306</v>
+        <v>502.019655033642</v>
       </c>
       <c r="K30" t="n">
-        <v>479.035796386456</v>
+        <v>472.540910877613</v>
       </c>
       <c r="L30" t="n">
-        <v>451.559062637155</v>
+        <v>425.183631561892</v>
       </c>
     </row>
   </sheetData>
@@ -1661,34 +1661,34 @@
         <v>2164.12210757737</v>
       </c>
       <c r="C2" t="n">
-        <v>2077.86797519044</v>
+        <v>2077.45998827981</v>
       </c>
       <c r="D2" t="n">
-        <v>1991.07522985628</v>
+        <v>1990.17668022254</v>
       </c>
       <c r="E2" t="n">
-        <v>1903.9599060717</v>
+        <v>1903.64179686904</v>
       </c>
       <c r="F2" t="n">
-        <v>1816.89389864766</v>
+        <v>1816.99848742985</v>
       </c>
       <c r="G2" t="n">
-        <v>1730.46217150244</v>
+        <v>1732.0012741492</v>
       </c>
       <c r="H2" t="n">
-        <v>1645.52423328809</v>
+        <v>1643.98450219585</v>
       </c>
       <c r="I2" t="n">
-        <v>1557.70500929419</v>
+        <v>1558.22274731672</v>
       </c>
       <c r="J2" t="n">
-        <v>1471.68745400197</v>
+        <v>1470.07337035252</v>
       </c>
       <c r="K2" t="n">
-        <v>1386.15223917463</v>
+        <v>1386.53889040341</v>
       </c>
       <c r="L2" t="n">
-        <v>1298.32950399431</v>
+        <v>1298.39795867749</v>
       </c>
     </row>
     <row r="3">
@@ -1699,34 +1699,34 @@
         <v>1635.30126530936</v>
       </c>
       <c r="C3" t="n">
-        <v>1571.09604333271</v>
+        <v>1571.54176391563</v>
       </c>
       <c r="D3" t="n">
-        <v>1506.20556699697</v>
+        <v>1502.03427688338</v>
       </c>
       <c r="E3" t="n">
-        <v>1437.10151616283</v>
+        <v>1437.80420684571</v>
       </c>
       <c r="F3" t="n">
-        <v>1372.52488959618</v>
+        <v>1370.65065020434</v>
       </c>
       <c r="G3" t="n">
-        <v>1313.35866806983</v>
+        <v>1307.64139815363</v>
       </c>
       <c r="H3" t="n">
-        <v>1242.19768437564</v>
+        <v>1241.48777391298</v>
       </c>
       <c r="I3" t="n">
-        <v>1178.20654574904</v>
+        <v>1176.28686460182</v>
       </c>
       <c r="J3" t="n">
-        <v>1110.79593984588</v>
+        <v>1108.34022345443</v>
       </c>
       <c r="K3" t="n">
-        <v>1050.61253894846</v>
+        <v>1046.68036258162</v>
       </c>
       <c r="L3" t="n">
-        <v>982.908601698045</v>
+        <v>981.446809675501</v>
       </c>
     </row>
     <row r="4">
@@ -1737,34 +1737,34 @@
         <v>1535.66030212568</v>
       </c>
       <c r="C4" t="n">
-        <v>1473.00549247973</v>
+        <v>1472.26107388261</v>
       </c>
       <c r="D4" t="n">
-        <v>1414.18722880273</v>
+        <v>1412.67978925677</v>
       </c>
       <c r="E4" t="n">
-        <v>1350.44033760921</v>
+        <v>1354.18302814539</v>
       </c>
       <c r="F4" t="n">
-        <v>1289.02326770569</v>
+        <v>1289.74638754842</v>
       </c>
       <c r="G4" t="n">
-        <v>1229.73345812777</v>
+        <v>1225.52333764586</v>
       </c>
       <c r="H4" t="n">
-        <v>1169.02752764942</v>
+        <v>1173.36723635455</v>
       </c>
       <c r="I4" t="n">
-        <v>1106.30338565283</v>
+        <v>1104.20633882957</v>
       </c>
       <c r="J4" t="n">
-        <v>1041.92721867859</v>
+        <v>1048.35412124538</v>
       </c>
       <c r="K4" t="n">
-        <v>979.060752152668</v>
+        <v>984.894337368296</v>
       </c>
       <c r="L4" t="n">
-        <v>922.19136416149</v>
+        <v>922.301860805094</v>
       </c>
     </row>
     <row r="5">
@@ -1775,34 +1775,34 @@
         <v>1447.55759996177</v>
       </c>
       <c r="C5" t="n">
-        <v>1390.23250899494</v>
+        <v>1387.11025642606</v>
       </c>
       <c r="D5" t="n">
-        <v>1328.59963225828</v>
+        <v>1333.0708375848</v>
       </c>
       <c r="E5" t="n">
-        <v>1273.25081536288</v>
+        <v>1273.3242400348</v>
       </c>
       <c r="F5" t="n">
-        <v>1217.05521919775</v>
+        <v>1218.92974557932</v>
       </c>
       <c r="G5" t="n">
-        <v>1161.31757112912</v>
+        <v>1153.03464376606</v>
       </c>
       <c r="H5" t="n">
-        <v>1094.73197604983</v>
+        <v>1099.1889665995</v>
       </c>
       <c r="I5" t="n">
-        <v>1037.65914054403</v>
+        <v>1039.77793806956</v>
       </c>
       <c r="J5" t="n">
-        <v>989.381316065271</v>
+        <v>984.618719883795</v>
       </c>
       <c r="K5" t="n">
-        <v>923.851336117718</v>
+        <v>925.837949048938</v>
       </c>
       <c r="L5" t="n">
-        <v>874.063834533427</v>
+        <v>875.234799392388</v>
       </c>
     </row>
     <row r="6">
@@ -1813,34 +1813,34 @@
         <v>1213.76973914927</v>
       </c>
       <c r="C6" t="n">
-        <v>1163.08947812446</v>
+        <v>1165.94871510887</v>
       </c>
       <c r="D6" t="n">
-        <v>1114.28454904981</v>
+        <v>1116.36406396804</v>
       </c>
       <c r="E6" t="n">
-        <v>1068.10743761233</v>
+        <v>1067.22184097481</v>
       </c>
       <c r="F6" t="n">
-        <v>1019.40100691761</v>
+        <v>1020.0757046544</v>
       </c>
       <c r="G6" t="n">
-        <v>974.518026724879</v>
+        <v>972.091684605947</v>
       </c>
       <c r="H6" t="n">
-        <v>917.768232479827</v>
+        <v>924.646737645808</v>
       </c>
       <c r="I6" t="n">
-        <v>871.238042694201</v>
+        <v>871.097086998358</v>
       </c>
       <c r="J6" t="n">
-        <v>824.448011645072</v>
+        <v>825.98294643857</v>
       </c>
       <c r="K6" t="n">
-        <v>775.720684306099</v>
+        <v>775.511356505209</v>
       </c>
       <c r="L6" t="n">
-        <v>725.391738605369</v>
+        <v>725.653678188071</v>
       </c>
     </row>
     <row r="7">
@@ -1851,34 +1851,34 @@
         <v>1208.60085236847</v>
       </c>
       <c r="C7" t="n">
-        <v>1158.80886629501</v>
+        <v>1157.34523081492</v>
       </c>
       <c r="D7" t="n">
-        <v>1113.43736257658</v>
+        <v>1106.95444199883</v>
       </c>
       <c r="E7" t="n">
-        <v>1071.43303580712</v>
+        <v>1059.58188745507</v>
       </c>
       <c r="F7" t="n">
-        <v>1020.00585555565</v>
+        <v>1025.06382863408</v>
       </c>
       <c r="G7" t="n">
-        <v>963.492157638017</v>
+        <v>972.293080145746</v>
       </c>
       <c r="H7" t="n">
-        <v>920.484506776209</v>
+        <v>912.128981641988</v>
       </c>
       <c r="I7" t="n">
-        <v>865.384353662265</v>
+        <v>866.000361048773</v>
       </c>
       <c r="J7" t="n">
-        <v>816.277391855708</v>
+        <v>817.528379389443</v>
       </c>
       <c r="K7" t="n">
-        <v>779.513187209642</v>
+        <v>783.329070374554</v>
       </c>
       <c r="L7" t="n">
-        <v>722.689421461577</v>
+        <v>722.56599881917</v>
       </c>
     </row>
     <row r="8">
@@ -1889,34 +1889,34 @@
         <v>1134.13146662312</v>
       </c>
       <c r="C8" t="n">
-        <v>1087.97059800907</v>
+        <v>1090.36868980172</v>
       </c>
       <c r="D8" t="n">
-        <v>1040.09690802269</v>
+        <v>1043.90967781107</v>
       </c>
       <c r="E8" t="n">
-        <v>994.138626093682</v>
+        <v>998.444408808575</v>
       </c>
       <c r="F8" t="n">
-        <v>945.439443424822</v>
+        <v>957.702300898731</v>
       </c>
       <c r="G8" t="n">
-        <v>905.437542831258</v>
+        <v>904.490646190493</v>
       </c>
       <c r="H8" t="n">
-        <v>861.889571033541</v>
+        <v>863.189046982023</v>
       </c>
       <c r="I8" t="n">
-        <v>820.310208532517</v>
+        <v>814.306014147946</v>
       </c>
       <c r="J8" t="n">
-        <v>770.990056849982</v>
+        <v>774.169242955847</v>
       </c>
       <c r="K8" t="n">
-        <v>724.580455705322</v>
+        <v>726.17068347236</v>
       </c>
       <c r="L8" t="n">
-        <v>677.034464461666</v>
+        <v>680.954788125126</v>
       </c>
     </row>
     <row r="9">
@@ -1927,34 +1927,34 @@
         <v>1064.0668085538</v>
       </c>
       <c r="C9" t="n">
-        <v>1021.72662899731</v>
+        <v>1021.7325995489</v>
       </c>
       <c r="D9" t="n">
-        <v>980.504445034258</v>
+        <v>981.064253658761</v>
       </c>
       <c r="E9" t="n">
-        <v>941.684072669157</v>
+        <v>937.821565519479</v>
       </c>
       <c r="F9" t="n">
-        <v>891.781146983072</v>
+        <v>894.002697712421</v>
       </c>
       <c r="G9" t="n">
-        <v>853.120393984122</v>
+        <v>852.186182028664</v>
       </c>
       <c r="H9" t="n">
-        <v>808.501213331462</v>
+        <v>809.426768458527</v>
       </c>
       <c r="I9" t="n">
-        <v>766.154901135224</v>
+        <v>766.363080812395</v>
       </c>
       <c r="J9" t="n">
-        <v>717.237817499586</v>
+        <v>725.579393842116</v>
       </c>
       <c r="K9" t="n">
-        <v>682.947528518255</v>
+        <v>675.627393382618</v>
       </c>
       <c r="L9" t="n">
-        <v>639.065936740942</v>
+        <v>636.218748893742</v>
       </c>
     </row>
     <row r="10">
@@ -1965,34 +1965,34 @@
         <v>1003.70926718899</v>
       </c>
       <c r="C10" t="n">
-        <v>962.447379229273</v>
+        <v>962.706216445162</v>
       </c>
       <c r="D10" t="n">
-        <v>925.844097720107</v>
+        <v>924.618545554421</v>
       </c>
       <c r="E10" t="n">
-        <v>885.153430183477</v>
+        <v>883.150787066396</v>
       </c>
       <c r="F10" t="n">
-        <v>843.713375468625</v>
+        <v>841.341279296358</v>
       </c>
       <c r="G10" t="n">
-        <v>805.094846905086</v>
+        <v>805.56907943986</v>
       </c>
       <c r="H10" t="n">
-        <v>759.858106513256</v>
+        <v>756.141949501733</v>
       </c>
       <c r="I10" t="n">
-        <v>721.119389775132</v>
+        <v>721.676523804145</v>
       </c>
       <c r="J10" t="n">
-        <v>678.242893271769</v>
+        <v>682.609564874351</v>
       </c>
       <c r="K10" t="n">
-        <v>643.890416192649</v>
+        <v>641.940410627878</v>
       </c>
       <c r="L10" t="n">
-        <v>606.875902032938</v>
+        <v>596.252840611297</v>
       </c>
     </row>
     <row r="11">
@@ -2003,34 +2003,34 @@
         <v>971.888494642035</v>
       </c>
       <c r="C11" t="n">
-        <v>934.641231837981</v>
+        <v>933.993599327185</v>
       </c>
       <c r="D11" t="n">
-        <v>895.846078349757</v>
+        <v>893.726491371102</v>
       </c>
       <c r="E11" t="n">
-        <v>855.42232422441</v>
+        <v>855.677402365415</v>
       </c>
       <c r="F11" t="n">
-        <v>816.403048217542</v>
+        <v>817.581890983257</v>
       </c>
       <c r="G11" t="n">
-        <v>778.203580848397</v>
+        <v>777.987913452862</v>
       </c>
       <c r="H11" t="n">
-        <v>738.177246599873</v>
+        <v>737.361801296326</v>
       </c>
       <c r="I11" t="n">
-        <v>700.682541122668</v>
+        <v>698.606396475165</v>
       </c>
       <c r="J11" t="n">
-        <v>660.384695476764</v>
+        <v>659.698820994567</v>
       </c>
       <c r="K11" t="n">
-        <v>625.793128690037</v>
+        <v>624.671997982919</v>
       </c>
       <c r="L11" t="n">
-        <v>583.301163856816</v>
+        <v>582.289015756825</v>
       </c>
     </row>
     <row r="12">
@@ -2041,34 +2041,34 @@
         <v>960.826756659796</v>
       </c>
       <c r="C12" t="n">
-        <v>920.789873069886</v>
+        <v>924.450879539455</v>
       </c>
       <c r="D12" t="n">
-        <v>885.418012661712</v>
+        <v>883.669618458817</v>
       </c>
       <c r="E12" t="n">
-        <v>850.384705574284</v>
+        <v>850.623698873961</v>
       </c>
       <c r="F12" t="n">
-        <v>814.384681231847</v>
+        <v>809.885514138464</v>
       </c>
       <c r="G12" t="n">
-        <v>771.120027759832</v>
+        <v>768.426732263881</v>
       </c>
       <c r="H12" t="n">
-        <v>733.350531143488</v>
+        <v>724.97545018123</v>
       </c>
       <c r="I12" t="n">
-        <v>691.743387966919</v>
+        <v>695.775975759868</v>
       </c>
       <c r="J12" t="n">
-        <v>663.689612658368</v>
+        <v>646.585744586844</v>
       </c>
       <c r="K12" t="n">
-        <v>615.456753393515</v>
+        <v>617.13591834808</v>
       </c>
       <c r="L12" t="n">
-        <v>577.718290545577</v>
+        <v>582.775274236908</v>
       </c>
     </row>
     <row r="13">
@@ -2079,34 +2079,34 @@
         <v>922.812449138863</v>
       </c>
       <c r="C13" t="n">
-        <v>884.683235684039</v>
+        <v>884.513098603221</v>
       </c>
       <c r="D13" t="n">
-        <v>850.09614814576</v>
+        <v>849.477662237712</v>
       </c>
       <c r="E13" t="n">
-        <v>813.188835703586</v>
+        <v>812.656604321167</v>
       </c>
       <c r="F13" t="n">
-        <v>777.469631622516</v>
+        <v>779.518104140599</v>
       </c>
       <c r="G13" t="n">
-        <v>738.085362683042</v>
+        <v>740.172567288331</v>
       </c>
       <c r="H13" t="n">
-        <v>700.953543086587</v>
+        <v>701.856558231943</v>
       </c>
       <c r="I13" t="n">
-        <v>664.542554648729</v>
+        <v>664.600735394706</v>
       </c>
       <c r="J13" t="n">
-        <v>629.851470098136</v>
+        <v>629.197015552133</v>
       </c>
       <c r="K13" t="n">
-        <v>588.598405808954</v>
+        <v>588.22471721631</v>
       </c>
       <c r="L13" t="n">
-        <v>555.810922841832</v>
+        <v>551.483481277335</v>
       </c>
     </row>
     <row r="14">
@@ -2117,34 +2117,34 @@
         <v>894.390673057778</v>
       </c>
       <c r="C14" t="n">
-        <v>857.846929918707</v>
+        <v>857.540064718962</v>
       </c>
       <c r="D14" t="n">
-        <v>823.230122338017</v>
+        <v>823.835129148556</v>
       </c>
       <c r="E14" t="n">
-        <v>789.641453899485</v>
+        <v>787.053323481577</v>
       </c>
       <c r="F14" t="n">
-        <v>752.515582922235</v>
+        <v>749.127752132263</v>
       </c>
       <c r="G14" t="n">
-        <v>713.787953874614</v>
+        <v>713.488231904477</v>
       </c>
       <c r="H14" t="n">
-        <v>682.06045257241</v>
+        <v>679.983665988679</v>
       </c>
       <c r="I14" t="n">
-        <v>640.639669858192</v>
+        <v>644.407309151664</v>
       </c>
       <c r="J14" t="n">
-        <v>607.658837780142</v>
+        <v>608.45244632679</v>
       </c>
       <c r="K14" t="n">
-        <v>573.784243273828</v>
+        <v>566.954143785047</v>
       </c>
       <c r="L14" t="n">
-        <v>534.050229508353</v>
+        <v>533.197754497489</v>
       </c>
     </row>
     <row r="15">
@@ -2155,34 +2155,34 @@
         <v>881.709431112267</v>
       </c>
       <c r="C15" t="n">
-        <v>850.083193289462</v>
+        <v>851.125157981504</v>
       </c>
       <c r="D15" t="n">
-        <v>811.147079814889</v>
+        <v>811.499010983685</v>
       </c>
       <c r="E15" t="n">
-        <v>778.674207829442</v>
+        <v>767.427224080364</v>
       </c>
       <c r="F15" t="n">
-        <v>744.109105358757</v>
+        <v>731.918856939527</v>
       </c>
       <c r="G15" t="n">
-        <v>702.383336064139</v>
+        <v>702.214866727416</v>
       </c>
       <c r="H15" t="n">
-        <v>677.717313645243</v>
+        <v>670.827362407033</v>
       </c>
       <c r="I15" t="n">
-        <v>629.271584681043</v>
+        <v>640.214731230209</v>
       </c>
       <c r="J15" t="n">
-        <v>599.552529401315</v>
+        <v>604.559328935412</v>
       </c>
       <c r="K15" t="n">
-        <v>561.504151078921</v>
+        <v>565.736367608037</v>
       </c>
       <c r="L15" t="n">
-        <v>529.409913785921</v>
+        <v>517.43041951461</v>
       </c>
     </row>
     <row r="16">
@@ -2193,34 +2193,34 @@
         <v>881.459179778996</v>
       </c>
       <c r="C16" t="n">
-        <v>848.037643476201</v>
+        <v>846.650164138663</v>
       </c>
       <c r="D16" t="n">
-        <v>810.706504939523</v>
+        <v>808.906727415791</v>
       </c>
       <c r="E16" t="n">
-        <v>773.569191450492</v>
+        <v>778.114458316165</v>
       </c>
       <c r="F16" t="n">
-        <v>738.658590871652</v>
+        <v>740.999695283501</v>
       </c>
       <c r="G16" t="n">
-        <v>700.671128013443</v>
+        <v>704.345782339381</v>
       </c>
       <c r="H16" t="n">
-        <v>663.844563804505</v>
+        <v>667.679190703191</v>
       </c>
       <c r="I16" t="n">
-        <v>637.709733987517</v>
+        <v>632.646189332567</v>
       </c>
       <c r="J16" t="n">
-        <v>595.029229318065</v>
+        <v>598.892431260271</v>
       </c>
       <c r="K16" t="n">
-        <v>563.151760358478</v>
+        <v>563.945370406713</v>
       </c>
       <c r="L16" t="n">
-        <v>531.041607637737</v>
+        <v>529.323201203192</v>
       </c>
     </row>
     <row r="17">
@@ -2231,34 +2231,34 @@
         <v>877.183591212414</v>
       </c>
       <c r="C17" t="n">
-        <v>837.309421679317</v>
+        <v>842.566106564726</v>
       </c>
       <c r="D17" t="n">
-        <v>803.466246348484</v>
+        <v>801.039090503872</v>
       </c>
       <c r="E17" t="n">
-        <v>770.685168303928</v>
+        <v>769.452986076735</v>
       </c>
       <c r="F17" t="n">
-        <v>738.003702308346</v>
+        <v>747.770813964629</v>
       </c>
       <c r="G17" t="n">
-        <v>700.983465037012</v>
+        <v>705.053604702088</v>
       </c>
       <c r="H17" t="n">
-        <v>667.289131935722</v>
+        <v>666.805248145799</v>
       </c>
       <c r="I17" t="n">
-        <v>629.792794456657</v>
+        <v>631.27340270957</v>
       </c>
       <c r="J17" t="n">
-        <v>596.184020362428</v>
+        <v>599.620898882296</v>
       </c>
       <c r="K17" t="n">
-        <v>560.515836135774</v>
+        <v>576.192080058308</v>
       </c>
       <c r="L17" t="n">
-        <v>515.620937502799</v>
+        <v>534.432196210641</v>
       </c>
     </row>
     <row r="18">
@@ -2269,34 +2269,34 @@
         <v>848.938617637658</v>
       </c>
       <c r="C18" t="n">
-        <v>815.988681662081</v>
+        <v>815.455358662727</v>
       </c>
       <c r="D18" t="n">
-        <v>780.552176789997</v>
+        <v>782.732432712068</v>
       </c>
       <c r="E18" t="n">
-        <v>752.062163244206</v>
+        <v>743.051910827648</v>
       </c>
       <c r="F18" t="n">
-        <v>714.197449467377</v>
+        <v>711.357265218365</v>
       </c>
       <c r="G18" t="n">
-        <v>681.297320719132</v>
+        <v>678.211891514025</v>
       </c>
       <c r="H18" t="n">
-        <v>646.549337823093</v>
+        <v>645.674203008606</v>
       </c>
       <c r="I18" t="n">
-        <v>613.820837419008</v>
+        <v>614.162853137298</v>
       </c>
       <c r="J18" t="n">
-        <v>576.987609234003</v>
+        <v>580.241235937573</v>
       </c>
       <c r="K18" t="n">
-        <v>542.437184248378</v>
+        <v>548.020489744987</v>
       </c>
       <c r="L18" t="n">
-        <v>510.668403876246</v>
+        <v>508.412500928728</v>
       </c>
     </row>
     <row r="19">
@@ -2307,34 +2307,34 @@
         <v>846.851140715077</v>
       </c>
       <c r="C19" t="n">
-        <v>812.229532346011</v>
+        <v>813.220778672341</v>
       </c>
       <c r="D19" t="n">
-        <v>779.891703339549</v>
+        <v>779.875802221307</v>
       </c>
       <c r="E19" t="n">
-        <v>742.991019750669</v>
+        <v>747.294185946915</v>
       </c>
       <c r="F19" t="n">
-        <v>705.426590006358</v>
+        <v>712.598127081423</v>
       </c>
       <c r="G19" t="n">
-        <v>672.931818252293</v>
+        <v>669.55697102222</v>
       </c>
       <c r="H19" t="n">
-        <v>638.407054622639</v>
+        <v>652.859445193718</v>
       </c>
       <c r="I19" t="n">
-        <v>612.385407212854</v>
+        <v>606.577173413562</v>
       </c>
       <c r="J19" t="n">
-        <v>570.728641608068</v>
+        <v>577.119772395009</v>
       </c>
       <c r="K19" t="n">
-        <v>545.197086592041</v>
+        <v>538.482102767028</v>
       </c>
       <c r="L19" t="n">
-        <v>502.214437376566</v>
+        <v>513.499096146998</v>
       </c>
     </row>
     <row r="20">
@@ -2345,34 +2345,34 @@
         <v>846.462282116047</v>
       </c>
       <c r="C20" t="n">
-        <v>811.328770136451</v>
+        <v>813.717471138646</v>
       </c>
       <c r="D20" t="n">
-        <v>778.185307602273</v>
+        <v>779.185367572477</v>
       </c>
       <c r="E20" t="n">
-        <v>750.214964867856</v>
+        <v>748.127351057085</v>
       </c>
       <c r="F20" t="n">
-        <v>706.653695076153</v>
+        <v>713.616904223294</v>
       </c>
       <c r="G20" t="n">
-        <v>676.055593125851</v>
+        <v>684.133282553182</v>
       </c>
       <c r="H20" t="n">
-        <v>639.389012504524</v>
+        <v>642.275291186</v>
       </c>
       <c r="I20" t="n">
-        <v>613.305918574973</v>
+        <v>613.091974326919</v>
       </c>
       <c r="J20" t="n">
-        <v>575.477479635422</v>
+        <v>566.316846528558</v>
       </c>
       <c r="K20" t="n">
-        <v>529.076064825528</v>
+        <v>537.15083001591</v>
       </c>
       <c r="L20" t="n">
-        <v>507.466117792841</v>
+        <v>500.369758692751</v>
       </c>
     </row>
     <row r="21">
@@ -2383,34 +2383,34 @@
         <v>832.477887453572</v>
       </c>
       <c r="C21" t="n">
-        <v>799.807024910781</v>
+        <v>798.995685963808</v>
       </c>
       <c r="D21" t="n">
-        <v>766.881379144818</v>
+        <v>766.251727781371</v>
       </c>
       <c r="E21" t="n">
-        <v>730.882158508638</v>
+        <v>733.344155435681</v>
       </c>
       <c r="F21" t="n">
-        <v>698.175611762336</v>
+        <v>701.87958586778</v>
       </c>
       <c r="G21" t="n">
-        <v>664.168114621561</v>
+        <v>666.270939460474</v>
       </c>
       <c r="H21" t="n">
-        <v>631.410772191963</v>
+        <v>634.503785337219</v>
       </c>
       <c r="I21" t="n">
-        <v>597.283994675261</v>
+        <v>597.364596095754</v>
       </c>
       <c r="J21" t="n">
-        <v>567.102062678137</v>
+        <v>564.283183791803</v>
       </c>
       <c r="K21" t="n">
-        <v>533.322083734758</v>
+        <v>531.641036928923</v>
       </c>
       <c r="L21" t="n">
-        <v>500.447421892456</v>
+        <v>504.010422893519</v>
       </c>
     </row>
     <row r="22">
@@ -2421,34 +2421,34 @@
         <v>822.563748604459</v>
       </c>
       <c r="C22" t="n">
-        <v>792.174734749448</v>
+        <v>793.855283573119</v>
       </c>
       <c r="D22" t="n">
-        <v>755.266836771745</v>
+        <v>750.275752183139</v>
       </c>
       <c r="E22" t="n">
-        <v>723.32970778607</v>
+        <v>725.44749016234</v>
       </c>
       <c r="F22" t="n">
-        <v>696.188809470402</v>
+        <v>680.410151245928</v>
       </c>
       <c r="G22" t="n">
-        <v>664.065405439462</v>
+        <v>666.243447731707</v>
       </c>
       <c r="H22" t="n">
-        <v>624.357118651405</v>
+        <v>615.134798790905</v>
       </c>
       <c r="I22" t="n">
-        <v>586.124645782995</v>
+        <v>592.369458794067</v>
       </c>
       <c r="J22" t="n">
-        <v>555.839721729439</v>
+        <v>558.593100655073</v>
       </c>
       <c r="K22" t="n">
-        <v>533.781365777585</v>
+        <v>523.632124086187</v>
       </c>
       <c r="L22" t="n">
-        <v>502.787415252431</v>
+        <v>505.857563416582</v>
       </c>
     </row>
     <row r="23">
@@ -2459,34 +2459,34 @@
         <v>782.351538821256</v>
       </c>
       <c r="C23" t="n">
-        <v>756.461709299867</v>
+        <v>751.636971774136</v>
       </c>
       <c r="D23" t="n">
-        <v>722.925406337797</v>
+        <v>718.586930544079</v>
       </c>
       <c r="E23" t="n">
-        <v>679.071468739126</v>
+        <v>687.35225607706</v>
       </c>
       <c r="F23" t="n">
-        <v>647.425063376808</v>
+        <v>661.055497028976</v>
       </c>
       <c r="G23" t="n">
-        <v>623.839311309938</v>
+        <v>625.394685183122</v>
       </c>
       <c r="H23" t="n">
-        <v>607.975451388453</v>
+        <v>589.851730212447</v>
       </c>
       <c r="I23" t="n">
-        <v>563.78144425233</v>
+        <v>558.237194941032</v>
       </c>
       <c r="J23" t="n">
-        <v>533.373366120679</v>
+        <v>533.471208332831</v>
       </c>
       <c r="K23" t="n">
-        <v>515.37927939676</v>
+        <v>503.050332099105</v>
       </c>
       <c r="L23" t="n">
-        <v>464.870588160007</v>
+        <v>457.670196056606</v>
       </c>
     </row>
     <row r="24">
@@ -2497,34 +2497,34 @@
         <v>756.452566074208</v>
       </c>
       <c r="C24" t="n">
-        <v>730.125939502598</v>
+        <v>730.272400457248</v>
       </c>
       <c r="D24" t="n">
-        <v>693.115236249877</v>
+        <v>688.949966610341</v>
       </c>
       <c r="E24" t="n">
-        <v>662.557581235783</v>
+        <v>658.363846638761</v>
       </c>
       <c r="F24" t="n">
-        <v>643.707529449862</v>
+        <v>635.96843545343</v>
       </c>
       <c r="G24" t="n">
-        <v>611.389055791006</v>
+        <v>595.808318021239</v>
       </c>
       <c r="H24" t="n">
-        <v>576.613954909122</v>
+        <v>573.815065982048</v>
       </c>
       <c r="I24" t="n">
-        <v>550.207068266627</v>
+        <v>535.65817909254</v>
       </c>
       <c r="J24" t="n">
-        <v>520.767245315067</v>
+        <v>520.941608891887</v>
       </c>
       <c r="K24" t="n">
-        <v>488.543256101723</v>
+        <v>480.885716615161</v>
       </c>
       <c r="L24" t="n">
-        <v>441.207465401643</v>
+        <v>444.598200727019</v>
       </c>
     </row>
     <row r="25">
@@ -2535,34 +2535,34 @@
         <v>685.965465828145</v>
       </c>
       <c r="C25" t="n">
-        <v>653.151686011338</v>
+        <v>655.304182381148</v>
       </c>
       <c r="D25" t="n">
-        <v>626.298385971192</v>
+        <v>631.667250580943</v>
       </c>
       <c r="E25" t="n">
-        <v>599.592571275386</v>
+        <v>607.005134693883</v>
       </c>
       <c r="F25" t="n">
-        <v>570.184856820403</v>
+        <v>575.976616484809</v>
       </c>
       <c r="G25" t="n">
-        <v>536.824946867834</v>
+        <v>549.369724924357</v>
       </c>
       <c r="H25" t="n">
-        <v>512.290385433177</v>
+        <v>526.209866617441</v>
       </c>
       <c r="I25" t="n">
-        <v>496.759513736368</v>
+        <v>507.30650466384</v>
       </c>
       <c r="J25" t="n">
-        <v>455.050404314151</v>
+        <v>447.349165595815</v>
       </c>
       <c r="K25" t="n">
-        <v>430.224637915646</v>
+        <v>423.83663911486</v>
       </c>
       <c r="L25" t="n">
-        <v>409.73650620677</v>
+        <v>406.129207472973</v>
       </c>
     </row>
     <row r="26">
@@ -2573,34 +2573,34 @@
         <v>680.5409390451</v>
       </c>
       <c r="C26" t="n">
-        <v>648.993466422504</v>
+        <v>649.54223094895</v>
       </c>
       <c r="D26" t="n">
-        <v>625.084449608349</v>
+        <v>627.507238091794</v>
       </c>
       <c r="E26" t="n">
-        <v>597.816468955034</v>
+        <v>595.638713396042</v>
       </c>
       <c r="F26" t="n">
-        <v>573.532031462895</v>
+        <v>579.440474461232</v>
       </c>
       <c r="G26" t="n">
-        <v>555.097146583611</v>
+        <v>541.079310683518</v>
       </c>
       <c r="H26" t="n">
-        <v>513.922241015808</v>
+        <v>518.343053216841</v>
       </c>
       <c r="I26" t="n">
-        <v>491.838058671205</v>
+        <v>483.550973923908</v>
       </c>
       <c r="J26" t="n">
-        <v>467.524558933637</v>
+        <v>462.797552974156</v>
       </c>
       <c r="K26" t="n">
-        <v>439.577176364545</v>
+        <v>428.749714449193</v>
       </c>
       <c r="L26" t="n">
-        <v>407.602609652577</v>
+        <v>417.076886436759</v>
       </c>
     </row>
     <row r="27">
@@ -2611,34 +2611,34 @@
         <v>675.93934039216</v>
       </c>
       <c r="C27" t="n">
-        <v>649.310909369847</v>
+        <v>641.639939052456</v>
       </c>
       <c r="D27" t="n">
-        <v>616.893001289624</v>
+        <v>621.340912139738</v>
       </c>
       <c r="E27" t="n">
-        <v>592.5221309007</v>
+        <v>597.92615468826</v>
       </c>
       <c r="F27" t="n">
-        <v>565.653026005686</v>
+        <v>568.771531360284</v>
       </c>
       <c r="G27" t="n">
-        <v>541.634695670883</v>
+        <v>543.590493141768</v>
       </c>
       <c r="H27" t="n">
-        <v>517.847649368303</v>
+        <v>517.629947919079</v>
       </c>
       <c r="I27" t="n">
-        <v>498.382459752754</v>
+        <v>473.631541167787</v>
       </c>
       <c r="J27" t="n">
-        <v>466.58086213955</v>
+        <v>453.496959476064</v>
       </c>
       <c r="K27" t="n">
-        <v>428.774399408555</v>
+        <v>429.752913274291</v>
       </c>
       <c r="L27" t="n">
-        <v>403.902155029093</v>
+        <v>404.500743968514</v>
       </c>
     </row>
     <row r="28">
@@ -2649,34 +2649,34 @@
         <v>629.439880651951</v>
       </c>
       <c r="C28" t="n">
-        <v>601.180812961073</v>
+        <v>606.367215984634</v>
       </c>
       <c r="D28" t="n">
-        <v>577.919325523265</v>
+        <v>576.832013630555</v>
       </c>
       <c r="E28" t="n">
-        <v>554.453199230134</v>
+        <v>549.977075227892</v>
       </c>
       <c r="F28" t="n">
-        <v>523.399555210959</v>
+        <v>531.42533774896</v>
       </c>
       <c r="G28" t="n">
-        <v>504.199130704351</v>
+        <v>502.932259740386</v>
       </c>
       <c r="H28" t="n">
-        <v>477.016328873962</v>
+        <v>476.47010142236</v>
       </c>
       <c r="I28" t="n">
-        <v>456.257089468188</v>
+        <v>452.833014796246</v>
       </c>
       <c r="J28" t="n">
-        <v>425.72133132624</v>
+        <v>423.83065969971</v>
       </c>
       <c r="K28" t="n">
-        <v>394.435673373891</v>
+        <v>403.765352867821</v>
       </c>
       <c r="L28" t="n">
-        <v>381.275571009405</v>
+        <v>388.601167800265</v>
       </c>
     </row>
     <row r="29">
@@ -2687,34 +2687,34 @@
         <v>611.198261819082</v>
       </c>
       <c r="C29" t="n">
-        <v>586.944251864477</v>
+        <v>587.238330625839</v>
       </c>
       <c r="D29" t="n">
-        <v>560.989464740546</v>
+        <v>561.622687269171</v>
       </c>
       <c r="E29" t="n">
-        <v>536.4767804036</v>
+        <v>536.563963608237</v>
       </c>
       <c r="F29" t="n">
-        <v>513.315227767884</v>
+        <v>513.129764340821</v>
       </c>
       <c r="G29" t="n">
-        <v>488.673141800166</v>
+        <v>488.903953795282</v>
       </c>
       <c r="H29" t="n">
-        <v>464.291333844603</v>
+        <v>462.768156856473</v>
       </c>
       <c r="I29" t="n">
-        <v>440.802162978778</v>
+        <v>438.959253174864</v>
       </c>
       <c r="J29" t="n">
-        <v>414.793821703441</v>
+        <v>413.986351097227</v>
       </c>
       <c r="K29" t="n">
-        <v>391.619480325203</v>
+        <v>390.750395054678</v>
       </c>
       <c r="L29" t="n">
-        <v>366.625580519086</v>
+        <v>366.005277525228</v>
       </c>
     </row>
     <row r="30">
@@ -2725,34 +2725,34 @@
         <v>563.41643768302</v>
       </c>
       <c r="C30" t="n">
-        <v>542.462859391371</v>
+        <v>542.78909095269</v>
       </c>
       <c r="D30" t="n">
-        <v>516.788055380895</v>
+        <v>520.641655766323</v>
       </c>
       <c r="E30" t="n">
-        <v>497.001772690798</v>
+        <v>497.768246805857</v>
       </c>
       <c r="F30" t="n">
-        <v>470.367075704735</v>
+        <v>469.193491339318</v>
       </c>
       <c r="G30" t="n">
-        <v>446.414597010057</v>
+        <v>452.627890342998</v>
       </c>
       <c r="H30" t="n">
-        <v>421.762503320017</v>
+        <v>431.04060591944</v>
       </c>
       <c r="I30" t="n">
-        <v>405.439940740904</v>
+        <v>411.464733074082</v>
       </c>
       <c r="J30" t="n">
-        <v>378.377637601479</v>
+        <v>377.112074544491</v>
       </c>
       <c r="K30" t="n">
-        <v>367.526408380062</v>
+        <v>361.790480824727</v>
       </c>
       <c r="L30" t="n">
-        <v>349.789864117068</v>
+        <v>344.057684144686</v>
       </c>
     </row>
   </sheetData>
